--- a/config/gold-and-gears-generated/templates/GoldAndGearsContent.xlsx
+++ b/config/gold-and-gears-generated/templates/GoldAndGearsContent.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1653" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1649" uniqueCount="197">
   <si>
     <t>@table</t>
   </si>
@@ -381,7 +381,7 @@
     <t>GoldGearsOccurrenceChoice</t>
   </si>
   <si>
-    <t>31da02a5ff173585</t>
+    <t>8a53f53543d80007</t>
   </si>
   <si>
     <t>mechanism_quality</t>
@@ -444,7 +444,7 @@
     <t>GoldGearsService</t>
   </si>
   <si>
-    <t>1a237e83bf11271a</t>
+    <t>e0ed261042e55308</t>
   </si>
   <si>
     <t>source_ids</t>
@@ -471,7 +471,7 @@
     <t>GoldGearsAdventureOutcome</t>
   </si>
   <si>
-    <t>656ceb51e72e126a</t>
+    <t>c3bb8d34f39c9db5</t>
   </si>
   <si>
     <t>room_stable_key</t>
@@ -5440,7 +5440,7 @@
     <col min="11" max="11" width="28.7109375" style="5" customWidth="1"/>
     <col min="12" max="12" width="30.7109375" style="5" customWidth="1"/>
     <col min="13" max="14" width="22.7109375" style="5" customWidth="1"/>
-    <col min="15" max="15" width="30.7109375" style="5" customWidth="1"/>
+    <col min="15" max="15" width="17.7109375" style="5" customWidth="1"/>
     <col min="16" max="16" width="22.7109375" style="5" customWidth="1"/>
     <col min="17" max="17" width="12.7109375" style="5" customWidth="1"/>
     <col min="18" max="18" width="32.7109375" style="5" customWidth="1"/>
@@ -5743,7 +5743,7 @@
         <v>44</v>
       </c>
       <c r="O4" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="P4" s="5" t="s">
         <v>40</v>
@@ -5767,10 +5767,10 @@
         <v>44</v>
       </c>
       <c r="W4" s="5" t="s">
-        <v>40</v>
+        <v>137</v>
       </c>
       <c r="X4" s="5" t="s">
-        <v>40</v>
+        <v>137</v>
       </c>
       <c r="Y4" s="5" t="s">
         <v>40</v>
@@ -5944,7 +5944,9 @@
       <c r="N6" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="O6" s="5"/>
+      <c r="O6" s="5" t="s">
+        <v>51</v>
+      </c>
       <c r="P6" s="5" t="s">
         <v>71</v>
       </c>
@@ -5964,12 +5966,8 @@
       <c r="V6" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="W6" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="X6" s="5" t="s">
-        <v>58</v>
-      </c>
+      <c r="W6" s="5"/>
+      <c r="X6" s="5"/>
       <c r="Y6" s="5" t="s">
         <v>71</v>
       </c>
@@ -6038,7 +6036,7 @@
       <c r="AH7" s="6"/>
     </row>
   </sheetData>
-  <dataValidations count="8">
+  <dataValidations count="7">
     <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 2147483647." promptTitle="Integer range" prompt="Enter an integer from 1 to 2147483647." sqref="B8:B1007">
       <formula1>1</formula1>
       <formula2>2147483647</formula2>
@@ -6050,9 +6048,6 @@
       <formula1>"DataReady"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="GoldGearsEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
-      <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="GoldGearsEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="O8:O1007">
       <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
     <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Value outside range" error="Value must be an integer from 0 to 2147483647." promptTitle="Integer range" prompt="Enter an integer from 0 to 2147483647." sqref="S8:S1007">
@@ -6085,11 +6080,10 @@
     <col min="10" max="10" width="24.7109375" style="5" customWidth="1"/>
     <col min="11" max="11" width="28.7109375" style="5" customWidth="1"/>
     <col min="12" max="12" width="30.7109375" style="5" customWidth="1"/>
-    <col min="13" max="14" width="22.7109375" style="5" customWidth="1"/>
-    <col min="15" max="15" width="12.7109375" style="5" customWidth="1"/>
+    <col min="13" max="15" width="22.7109375" style="5" customWidth="1"/>
     <col min="16" max="16" width="17.7109375" style="5" customWidth="1"/>
-    <col min="17" max="18" width="12.7109375" style="5" customWidth="1"/>
-    <col min="19" max="19" width="16.7109375" style="5" customWidth="1"/>
+    <col min="17" max="17" width="12.7109375" style="5" customWidth="1"/>
+    <col min="18" max="19" width="16.7109375" style="5" customWidth="1"/>
     <col min="20" max="20" width="23.7109375" style="5" customWidth="1"/>
     <col min="21" max="21" width="22.7109375" style="5" customWidth="1"/>
     <col min="22" max="22" width="15.7109375" style="5" customWidth="1"/>
@@ -6328,7 +6322,7 @@
         <v>44</v>
       </c>
       <c r="O4" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="P4" s="5" t="s">
         <v>40</v>
@@ -6337,13 +6331,13 @@
         <v>40</v>
       </c>
       <c r="R4" s="5" t="s">
-        <v>40</v>
+        <v>137</v>
       </c>
       <c r="S4" s="5" t="s">
-        <v>40</v>
+        <v>137</v>
       </c>
       <c r="T4" s="5" t="s">
-        <v>40</v>
+        <v>137</v>
       </c>
       <c r="U4" s="5" t="s">
         <v>44</v>
@@ -6476,7 +6470,7 @@
         <v>54</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="P6" s="5" t="s">
         <v>50</v>
@@ -6484,15 +6478,9 @@
       <c r="Q6" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="R6" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="S6" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="T6" s="5" t="s">
-        <v>49</v>
-      </c>
+      <c r="R6" s="5"/>
+      <c r="S6" s="5"/>
+      <c r="T6" s="5"/>
       <c r="U6" s="5" t="s">
         <v>54</v>
       </c>
@@ -6572,7 +6560,7 @@
     <col min="11" max="11" width="28.7109375" style="5" customWidth="1"/>
     <col min="12" max="12" width="30.7109375" style="5" customWidth="1"/>
     <col min="13" max="14" width="22.7109375" style="5" customWidth="1"/>
-    <col min="15" max="15" width="30.7109375" style="5" customWidth="1"/>
+    <col min="15" max="15" width="17.7109375" style="5" customWidth="1"/>
     <col min="16" max="16" width="22.7109375" style="5" customWidth="1"/>
     <col min="17" max="17" width="12.7109375" style="5" customWidth="1"/>
     <col min="18" max="18" width="15.7109375" style="5" customWidth="1"/>
@@ -6850,7 +6838,7 @@
         <v>44</v>
       </c>
       <c r="O4" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="P4" s="5" t="s">
         <v>40</v>
@@ -6877,7 +6865,7 @@
         <v>40</v>
       </c>
       <c r="X4" s="5" t="s">
-        <v>40</v>
+        <v>137</v>
       </c>
       <c r="Y4" s="5" t="s">
         <v>40</v>
@@ -7027,7 +7015,9 @@
       <c r="N6" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="O6" s="5"/>
+      <c r="O6" s="5" t="s">
+        <v>51</v>
+      </c>
       <c r="P6" s="5" t="s">
         <v>71</v>
       </c>
@@ -7052,9 +7042,7 @@
       <c r="W6" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="X6" s="5" t="s">
-        <v>58</v>
-      </c>
+      <c r="X6" s="5"/>
       <c r="Y6" s="5" t="s">
         <v>51</v>
       </c>
@@ -7105,7 +7093,7 @@
       <c r="AD7" s="6"/>
     </row>
   </sheetData>
-  <dataValidations count="6">
+  <dataValidations count="5">
     <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 2147483647." promptTitle="Integer range" prompt="Enter an integer from 1 to 2147483647." sqref="B8:B1007">
       <formula1>1</formula1>
       <formula2>2147483647</formula2>
@@ -7119,9 +7107,6 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="GoldGearsEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
       <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="GoldGearsEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="O8:O1007">
-      <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid boolean value" error="Value must be true or false." promptTitle="Boolean" prompt="Select true or false." sqref="Z8:Z1007">
       <formula1>"true,false"</formula1>
     </dataValidation>
